--- a/config/ai_features.xlsx
+++ b/config/ai_features.xlsx
@@ -1,131 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ksang\eclipse-workspace\Aiccounting\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BBF479-B559-4FA6-9E21-16875E0FE242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Features" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Features" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
-  <si>
-    <t>AI Feature Routing — operator config (per AccGenie version)</t>
-  </si>
-  <si>
-    <t>byok = customer's own Anthropic key REQUIRED (locked without one). ag_key = uses AccGenie's key billed to the customer wallet, unless the customer has supplied their own key.</t>
-  </si>
-  <si>
-    <t>feature_id</t>
-  </si>
-  <si>
-    <t>class</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>document_recognition</t>
-  </si>
-  <si>
-    <t>byok</t>
-  </si>
-  <si>
-    <t>Reads PDFs/images. Heavy multi-call AI — customer's own key required.</t>
-  </si>
-  <si>
-    <t>bank_statement_ai</t>
-  </si>
-  <si>
-    <t>ag_key</t>
-  </si>
-  <si>
-    <t>Parses bank statements. Light/structured — AccGenie key + wallet.</t>
-  </si>
-  <si>
-    <t>ledger_statement_ai</t>
-  </si>
-  <si>
-    <t>Parses party ledger PDFs.</t>
-  </si>
-  <si>
-    <t>sales_ai_fill</t>
-  </si>
-  <si>
-    <t>Suggests sales-voucher line items from a description.</t>
-  </si>
-  <si>
-    <t>purchase_ai_fill</t>
-  </si>
-  <si>
-    <t>Suggests purchase-voucher line items.</t>
-  </si>
-  <si>
-    <t>ledger_suggest</t>
-  </si>
-  <si>
-    <t>Suggests likely Dr/Cr ledgers for a voucher row.</t>
-  </si>
-  <si>
-    <t>verbal_entry</t>
-  </si>
-  <si>
-    <t>Voice-to-voucher one-liner posting.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <i val="1"/>
+      <color rgb="00666666"/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2C5777"/>
-        <bgColor rgb="FF2C5777"/>
+        <fgColor rgb="002C5777"/>
+        <bgColor rgb="002C5777"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,54 +64,111 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -474,115 +456,167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AI Feature Routing — operator config (per AccGenie version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>byok = customer's own Anthropic key REQUIRED (locked without one). ag_key = uses AccGenie's key billed to the customer wallet, unless the customer has supplied their own key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>feature_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>document_recognition</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>byok</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Reads PDFs/images. Heavy multi-call AI — customer's own key required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>bank_statement_ai</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Parses bank statements. Light/structured — AccGenie key + wallet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ledger_statement_ai</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Parses party ledger PDFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>sales_ai_fill</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Suggests sales-voucher line items from a description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>purchase_ai_fill</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Suggests purchase-voucher line items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ledger_suggest</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Suggests likely Dr/Cr ledgers for a voucher row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>verbal_entry</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>ag_key</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Voice-to-voucher one-liner posting.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -591,7 +625,7 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="Invalid class" error="Must be 'byok' or 'ag_key'" sqref="B5:B11" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation sqref="B5:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid class" error="Must be 'byok' or 'ag_key'" type="list">
       <formula1>"byok,ag_key"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/ai_features.xlsx
+++ b/config/ai_features.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -616,6 +617,23 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Voice-to-voucher one-liner posting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>document_inbox</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>byok</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Document Inbox — classify+extract any incoming doc. Heavy multi-call AI; customer's own key required.</t>
         </is>
       </c>
     </row>

--- a/config/ai_features.xlsx
+++ b/config/ai_features.xlsx
@@ -509,12 +509,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>byok</t>
+          <t>ag_key</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Reads PDFs/images. Heavy multi-call AI — customer's own key required.</t>
+          <t>Reads PDFs/images. Built-in/wallet (AccGenie key + credits); never the customer key.</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Document Inbox — classify+extract any incoming doc. Heavy multi-call AI; customer's own key required.</t>
+          <t>Document Inbox — classify+extract any incoming doc. Heavy multi-call AI.</t>
         </is>
       </c>
     </row>

--- a/config/ai_features.xlsx
+++ b/config/ai_features.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -617,23 +617,6 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Voice-to-voucher one-liner posting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>document_inbox</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>byok</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Document Inbox — classify+extract any incoming doc. Heavy multi-call AI.</t>
         </is>
       </c>
     </row>
